--- a/tools/_out/airway_first_20261020/stage/04_DESIGN_TABLES/DesignTable_6504.xlsx
+++ b/tools/_out/airway_first_20261020/stage/04_DESIGN_TABLES/DesignTable_6504.xlsx
@@ -1430,12 +1430,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>[BRENNAN-CELL 2026-10-20: D1@BORE] Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Brennan TFA catalog p17 table TFA-p017-t05 "MJ-FJS STRAIGHT" row 6504-24-24 col "B1 DRILL" = 1.312 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan]</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>D (1) printed 1.38 (D (2) 1.31); copied as printed</t>
+          <t>D (1) printed 1.38 (D (2) 1.31); copied as printed | 2026-10-20 D1@BORE = Brennan 1.312 (Air-Way 1.38 cannot be built: Air-Way bore 1.38 &gt;= the -24 JIC tip dia 1.381 (generator BLOCKED))</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1446,6 +1446,11 @@
       <c r="Q16" t="inlineStr">
         <is>
           <t>6504-24-24</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
